--- a/survey_templates/028_network_security_evaluation_survey--survey_templates.xlsx
+++ b/survey_templates/028_network_security_evaluation_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,20 +515,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>network_security_evaluation_survey_page_1</t>
+          <t>network_security_evaluation_page_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Network Security Evaluation Survey</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>1. What is the current state of your organization's network segmentation?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please select from below options</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -538,7 +542,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,10 +552,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Network Security Evaluation</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>2. How do you rate the level of risk management in your organization?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please select from below options</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -571,10 +579,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Network Security Evaluation</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>3. What is the current state of your organization's security governance practices?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please select from below options</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -594,10 +606,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Network Security Evaluation</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>4. What is your current experience with the following security measures?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please select from below options</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -617,10 +633,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Network Security Evaluation</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>5. Are you using a formal risk assessment process?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Yes or No</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -630,7 +650,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,10 +660,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Network Security</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>6. How often do you perform regular security audits or assessments?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Select one of below options</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -653,7 +677,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,10 +687,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Network Security</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>7. What is your current level of awareness about common network threats?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please select from below options</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -686,10 +714,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Network Security</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>8. How many people in your organization have access to sensitive data?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please select from below options</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -699,7 +731,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,10 +741,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Network Security</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>9. Have you ever experienced a security breach or incident?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Yes or No</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -722,7 +758,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,10 +768,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Network Security</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>10. How quickly do you respond to security incidents?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Select one of below options</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -755,218 +795,15 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Network Security</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>11. What is your current budget for security measures?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please select from below options</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>network_security_evaluation_page_12</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Network Security</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>network_security_evaluation_page_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Network Security</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>network_security_evaluation_page_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Network Security</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>network_security_evaluation_page_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Network Security</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>network_security_evaluation_page_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Network Security</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>network_security_evaluation_page_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Network Security</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>network_security_evaluation_page_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Network Security</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>network_security_evaluation_page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Network Security</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>network_security_evaluation_page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Network Security</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -983,12 +820,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1011,160 +848,160 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_3_choices</t>
+          <t>network_security_evaluation_page_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>segmented_and_secure</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Segmented and secure</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_3_choices</t>
+          <t>network_security_evaluation_page_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>partially_segmented,_but_with_some_gaps</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Partially segmented, but with some gaps</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_3_choices</t>
+          <t>network_security_evaluation_page_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>not_segmented_at_all</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Not segmented at all</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_4_choices</t>
+          <t>network_security_evaluation_page_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>risk_management</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_4_choices</t>
+          <t>network_security_evaluation_page_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>security_governance</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Security Governance</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_4_choices</t>
+          <t>network_security_evaluation_page_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>asset_management</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Asset Management</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_5_choices</t>
+          <t>network_security_evaluation_page_3_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>mature_and_well-established</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Mature and well-established</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_5_choices</t>
+          <t>network_security_evaluation_page_3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>developing_but_not_yet_mature</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Developing but not yet mature</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_6_choices</t>
+          <t>network_security_evaluation_page_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>network_segmentation</t>
+          <t>basic_or_absent</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Network Segmentation</t>
+          <t>Basic or absent</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_6_choices</t>
+          <t>network_security_evaluation_page_4_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1174,721 +1011,415 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Network Segmentation</t>
+          <t>Network segmentation</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_6_choices</t>
+          <t>network_security_evaluation_page_4_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>network_segmentation</t>
+          <t>access_control_and_authentication</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Network Segmentation</t>
+          <t>Access control and authentication</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_7_choices</t>
+          <t>network_security_evaluation_page_4_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>encryption_and_data_protection</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Encryption and data protection</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_7_choices</t>
+          <t>network_security_evaluation_page_5_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_8_choices</t>
+          <t>network_security_evaluation_page_5_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>network_segmentation</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Network Segmentation</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_8_choices</t>
+          <t>network_security_evaluation_page_6_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>network_segmentation</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Network Segmentation</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_8_choices</t>
+          <t>network_security_evaluation_page_6_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>network_segmentation</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Network Segmentation</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_9_choices</t>
+          <t>network_security_evaluation_page_6_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>network_segmentation</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Network Segmentation</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_9_choices</t>
+          <t>network_security_evaluation_page_6_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>network_segmentation</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Network Segmentation</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_9_choices</t>
+          <t>network_security_evaluation_page_6_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>network_segmentation</t>
+          <t>yearly</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Network Segmentation</t>
+          <t>Yearly</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_10_choices</t>
+          <t>network_security_evaluation_page_7_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>network_segmentation</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Network Segmentation</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_10_choices</t>
+          <t>network_security_evaluation_page_7_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>network_segmentation</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Network Segmentation</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_10_choices</t>
+          <t>network_security_evaluation_page_7_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>network_segmentation</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Network Segmentation</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_11_choices</t>
+          <t>network_security_evaluation_page_8_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>network_segmentation</t>
+          <t>1-5_people</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Network Segmentation</t>
+          <t>1-5 people</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_11_choices</t>
+          <t>network_security_evaluation_page_8_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>network_segmentation</t>
+          <t>6-10_people</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Network Segmentation</t>
+          <t>6-10 people</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_11_choices</t>
+          <t>network_security_evaluation_page_8_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>network_segmentation</t>
+          <t>more_than_10_people</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Network Segmentation</t>
+          <t>More than 10 people</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_12_choices</t>
+          <t>network_security_evaluation_page_9_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>network_segmentation</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Network Segmentation</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_12_choices</t>
+          <t>network_security_evaluation_page_9_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>network_segmentation</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Network Segmentation</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_12_choices</t>
+          <t>network_security_evaluation_page_10_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>network_segmentation</t>
+          <t>immediately</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Network Segmentation</t>
+          <t>Immediately</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_13_choices</t>
+          <t>network_security_evaluation_page_10_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>network_segmentation</t>
+          <t>within_1_hour</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Network Segmentation</t>
+          <t>Within 1 hour</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_13_choices</t>
+          <t>network_security_evaluation_page_10_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>network_segmentation</t>
+          <t>within_1_day</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Network Segmentation</t>
+          <t>Within 1 day</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_13_choices</t>
+          <t>network_security_evaluation_page_10_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>network_segmentation</t>
+          <t>within_1_week</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Network Segmentation</t>
+          <t>Within 1 week</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_14_choices</t>
+          <t>network_security_evaluation_page_11_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>network_segmentation</t>
+          <t>&lt;_$10,000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Network Segmentation</t>
+          <t>&lt; $10,000</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_14_choices</t>
+          <t>network_security_evaluation_page_11_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>network_segmentation</t>
+          <t>$10,000-$50,000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Network Segmentation</t>
+          <t>$10,000-$50,000</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>network_security_evaluation_page_14_choices</t>
+          <t>network_security_evaluation_page_11_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>network_segmentation</t>
+          <t>$50,000-$100,000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Network Segmentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>network_security_evaluation_page_15_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>network_segmentation</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Network Segmentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>network_security_evaluation_page_15_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>network_segmentation</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Network Segmentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>network_security_evaluation_page_15_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>network_segmentation</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Network Segmentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>network_security_evaluation_page_16_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>network_segmentation</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Network Segmentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>network_security_evaluation_page_16_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>network_segmentation</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Network Segmentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>network_security_evaluation_page_16_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>network_segmentation</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Network Segmentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>network_security_evaluation_page_17_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>network_segmentation</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Network Segmentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>network_security_evaluation_page_17_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>network_segmentation</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Network Segmentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>network_security_evaluation_page_17_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>network_segmentation</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Network Segmentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>network_security_evaluation_page_18_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>network_segmentation</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Network Segmentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>network_security_evaluation_page_18_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>network_segmentation</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Network Segmentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>network_security_evaluation_page_18_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>network_segmentation</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Network Segmentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>network_security_evaluation_page_19_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>network_segmentation</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Network Segmentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>network_security_evaluation_page_19_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>network_segmentation</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Network Segmentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>network_security_evaluation_page_19_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>network_segmentation</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Network Segmentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>network_security_evaluation_page_20_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>network_segmentation</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Network Segmentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>network_security_evaluation_page_20_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>network_segmentation</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Network Segmentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>network_security_evaluation_page_20_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>network_segmentation</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Network Segmentation</t>
+          <t>$50,000-$100,000</t>
         </is>
       </c>
     </row>
